--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292EF899-CC2E-4B2B-8CEB-8CDF13A0608A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{737C2436-7891-458C-8579-E7676DEA5CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60600" yWindow="645" windowWidth="23610" windowHeight="9420" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57660" yWindow="5295" windowWidth="18630" windowHeight="9465" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -478,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P696"/>
+  <dimension ref="A1:P699"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -35188,103 +35188,253 @@
       </c>
     </row>
     <row r="695" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A695" s="5">
+      <c r="A695">
         <v>3765</v>
       </c>
-      <c r="B695" s="6">
-        <v>1</v>
-      </c>
-      <c r="C695" s="6">
-        <v>5</v>
-      </c>
-      <c r="D695" s="6">
-        <v>6</v>
-      </c>
-      <c r="E695" s="6">
-        <v>10</v>
-      </c>
-      <c r="F695" s="6">
-        <v>11</v>
-      </c>
-      <c r="G695" s="6">
-        <v>12</v>
-      </c>
-      <c r="H695" s="6">
-        <v>13</v>
-      </c>
-      <c r="I695" s="6">
-        <v>15</v>
-      </c>
-      <c r="J695" s="6">
-        <v>16</v>
-      </c>
-      <c r="K695" s="6">
-        <v>17</v>
-      </c>
-      <c r="L695" s="6">
-        <v>19</v>
-      </c>
-      <c r="M695" s="6">
-        <v>21</v>
-      </c>
-      <c r="N695" s="6">
-        <v>22</v>
-      </c>
-      <c r="O695" s="6">
-        <v>24</v>
-      </c>
-      <c r="P695" s="6">
+      <c r="B695">
+        <v>1</v>
+      </c>
+      <c r="C695">
+        <v>5</v>
+      </c>
+      <c r="D695">
+        <v>6</v>
+      </c>
+      <c r="E695">
+        <v>10</v>
+      </c>
+      <c r="F695">
+        <v>11</v>
+      </c>
+      <c r="G695">
+        <v>12</v>
+      </c>
+      <c r="H695">
+        <v>13</v>
+      </c>
+      <c r="I695">
+        <v>15</v>
+      </c>
+      <c r="J695">
+        <v>16</v>
+      </c>
+      <c r="K695">
+        <v>17</v>
+      </c>
+      <c r="L695">
+        <v>19</v>
+      </c>
+      <c r="M695">
+        <v>21</v>
+      </c>
+      <c r="N695">
+        <v>22</v>
+      </c>
+      <c r="O695">
+        <v>24</v>
+      </c>
+      <c r="P695">
         <v>25</v>
       </c>
     </row>
     <row r="696" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A696" s="5">
+      <c r="A696">
         <v>3766</v>
       </c>
-      <c r="B696" s="6">
-        <v>1</v>
-      </c>
-      <c r="C696" s="6">
-        <v>2</v>
-      </c>
-      <c r="D696" s="6">
-        <v>3</v>
-      </c>
-      <c r="E696" s="6">
-        <v>5</v>
-      </c>
-      <c r="F696" s="6">
-        <v>8</v>
-      </c>
-      <c r="G696" s="6">
-        <v>9</v>
-      </c>
-      <c r="H696" s="6">
-        <v>11</v>
-      </c>
-      <c r="I696" s="6">
-        <v>13</v>
-      </c>
-      <c r="J696" s="6">
-        <v>14</v>
-      </c>
-      <c r="K696" s="6">
-        <v>16</v>
-      </c>
-      <c r="L696" s="6">
-        <v>17</v>
-      </c>
-      <c r="M696" s="6">
-        <v>19</v>
-      </c>
-      <c r="N696" s="6">
-        <v>21</v>
-      </c>
-      <c r="O696" s="6">
-        <v>23</v>
-      </c>
-      <c r="P696" s="6">
-        <v>24</v>
+      <c r="B696">
+        <v>1</v>
+      </c>
+      <c r="C696">
+        <v>2</v>
+      </c>
+      <c r="D696">
+        <v>3</v>
+      </c>
+      <c r="E696">
+        <v>5</v>
+      </c>
+      <c r="F696">
+        <v>8</v>
+      </c>
+      <c r="G696">
+        <v>9</v>
+      </c>
+      <c r="H696">
+        <v>11</v>
+      </c>
+      <c r="I696">
+        <v>13</v>
+      </c>
+      <c r="J696">
+        <v>14</v>
+      </c>
+      <c r="K696">
+        <v>16</v>
+      </c>
+      <c r="L696">
+        <v>17</v>
+      </c>
+      <c r="M696">
+        <v>19</v>
+      </c>
+      <c r="N696">
+        <v>21</v>
+      </c>
+      <c r="O696">
+        <v>23</v>
+      </c>
+      <c r="P696">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="697" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A697" s="5">
+        <v>3767</v>
+      </c>
+      <c r="B697" s="6">
+        <v>2</v>
+      </c>
+      <c r="C697" s="6">
+        <v>4</v>
+      </c>
+      <c r="D697" s="6">
+        <v>6</v>
+      </c>
+      <c r="E697" s="6">
+        <v>7</v>
+      </c>
+      <c r="F697" s="6">
+        <v>9</v>
+      </c>
+      <c r="G697" s="6">
+        <v>10</v>
+      </c>
+      <c r="H697" s="6">
+        <v>11</v>
+      </c>
+      <c r="I697" s="6">
+        <v>13</v>
+      </c>
+      <c r="J697" s="6">
+        <v>14</v>
+      </c>
+      <c r="K697" s="6">
+        <v>15</v>
+      </c>
+      <c r="L697" s="6">
+        <v>16</v>
+      </c>
+      <c r="M697" s="6">
+        <v>20</v>
+      </c>
+      <c r="N697" s="6">
+        <v>21</v>
+      </c>
+      <c r="O697" s="6">
+        <v>22</v>
+      </c>
+      <c r="P697" s="6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="698" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A698" s="5">
+        <v>3768</v>
+      </c>
+      <c r="B698" s="6">
+        <v>2</v>
+      </c>
+      <c r="C698" s="6">
+        <v>3</v>
+      </c>
+      <c r="D698" s="6">
+        <v>4</v>
+      </c>
+      <c r="E698" s="6">
+        <v>5</v>
+      </c>
+      <c r="F698" s="6">
+        <v>6</v>
+      </c>
+      <c r="G698" s="6">
+        <v>7</v>
+      </c>
+      <c r="H698" s="6">
+        <v>10</v>
+      </c>
+      <c r="I698" s="6">
+        <v>11</v>
+      </c>
+      <c r="J698" s="6">
+        <v>12</v>
+      </c>
+      <c r="K698" s="6">
+        <v>14</v>
+      </c>
+      <c r="L698" s="6">
+        <v>15</v>
+      </c>
+      <c r="M698" s="6">
+        <v>17</v>
+      </c>
+      <c r="N698" s="6">
+        <v>20</v>
+      </c>
+      <c r="O698" s="6">
+        <v>23</v>
+      </c>
+      <c r="P698" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="699" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A699" s="5">
+        <v>3769</v>
+      </c>
+      <c r="B699" s="6">
+        <v>1</v>
+      </c>
+      <c r="C699" s="6">
+        <v>2</v>
+      </c>
+      <c r="D699" s="6">
+        <v>3</v>
+      </c>
+      <c r="E699" s="6">
+        <v>4</v>
+      </c>
+      <c r="F699" s="6">
+        <v>5</v>
+      </c>
+      <c r="G699" s="6">
+        <v>9</v>
+      </c>
+      <c r="H699" s="6">
+        <v>10</v>
+      </c>
+      <c r="I699" s="6">
+        <v>11</v>
+      </c>
+      <c r="J699" s="6">
+        <v>15</v>
+      </c>
+      <c r="K699" s="6">
+        <v>16</v>
+      </c>
+      <c r="L699" s="6">
+        <v>17</v>
+      </c>
+      <c r="M699" s="6">
+        <v>21</v>
+      </c>
+      <c r="N699" s="6">
+        <v>23</v>
+      </c>
+      <c r="O699" s="6">
+        <v>24</v>
+      </c>
+      <c r="P699" s="6">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -35293,6 +35443,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -35460,16 +35620,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -35480,6 +35630,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -35499,17 +35660,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{737C2436-7891-458C-8579-E7676DEA5CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B11CFC0-75A3-46B4-A9C3-EAB491A26E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57660" yWindow="5295" windowWidth="18630" windowHeight="9465" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="60300" yWindow="6345" windowWidth="24705" windowHeight="9000" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -148,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -156,8 +156,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P699"/>
+  <dimension ref="A1:P701"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -35288,152 +35286,252 @@
       </c>
     </row>
     <row r="697" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A697" s="5">
+      <c r="A697">
         <v>3767</v>
       </c>
-      <c r="B697" s="6">
-        <v>2</v>
-      </c>
-      <c r="C697" s="6">
-        <v>4</v>
-      </c>
-      <c r="D697" s="6">
-        <v>6</v>
-      </c>
-      <c r="E697" s="6">
-        <v>7</v>
-      </c>
-      <c r="F697" s="6">
-        <v>9</v>
-      </c>
-      <c r="G697" s="6">
-        <v>10</v>
-      </c>
-      <c r="H697" s="6">
-        <v>11</v>
-      </c>
-      <c r="I697" s="6">
-        <v>13</v>
-      </c>
-      <c r="J697" s="6">
-        <v>14</v>
-      </c>
-      <c r="K697" s="6">
-        <v>15</v>
-      </c>
-      <c r="L697" s="6">
-        <v>16</v>
-      </c>
-      <c r="M697" s="6">
-        <v>20</v>
-      </c>
-      <c r="N697" s="6">
-        <v>21</v>
-      </c>
-      <c r="O697" s="6">
-        <v>22</v>
-      </c>
-      <c r="P697" s="6">
+      <c r="B697">
+        <v>2</v>
+      </c>
+      <c r="C697">
+        <v>4</v>
+      </c>
+      <c r="D697">
+        <v>6</v>
+      </c>
+      <c r="E697">
+        <v>7</v>
+      </c>
+      <c r="F697">
+        <v>9</v>
+      </c>
+      <c r="G697">
+        <v>10</v>
+      </c>
+      <c r="H697">
+        <v>11</v>
+      </c>
+      <c r="I697">
+        <v>13</v>
+      </c>
+      <c r="J697">
+        <v>14</v>
+      </c>
+      <c r="K697">
+        <v>15</v>
+      </c>
+      <c r="L697">
+        <v>16</v>
+      </c>
+      <c r="M697">
+        <v>20</v>
+      </c>
+      <c r="N697">
+        <v>21</v>
+      </c>
+      <c r="O697">
+        <v>22</v>
+      </c>
+      <c r="P697">
         <v>23</v>
       </c>
     </row>
     <row r="698" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A698" s="5">
+      <c r="A698">
         <v>3768</v>
       </c>
-      <c r="B698" s="6">
-        <v>2</v>
-      </c>
-      <c r="C698" s="6">
-        <v>3</v>
-      </c>
-      <c r="D698" s="6">
-        <v>4</v>
-      </c>
-      <c r="E698" s="6">
-        <v>5</v>
-      </c>
-      <c r="F698" s="6">
-        <v>6</v>
-      </c>
-      <c r="G698" s="6">
-        <v>7</v>
-      </c>
-      <c r="H698" s="6">
-        <v>10</v>
-      </c>
-      <c r="I698" s="6">
-        <v>11</v>
-      </c>
-      <c r="J698" s="6">
-        <v>12</v>
-      </c>
-      <c r="K698" s="6">
-        <v>14</v>
-      </c>
-      <c r="L698" s="6">
-        <v>15</v>
-      </c>
-      <c r="M698" s="6">
-        <v>17</v>
-      </c>
-      <c r="N698" s="6">
-        <v>20</v>
-      </c>
-      <c r="O698" s="6">
-        <v>23</v>
-      </c>
-      <c r="P698" s="6">
+      <c r="B698">
+        <v>2</v>
+      </c>
+      <c r="C698">
+        <v>3</v>
+      </c>
+      <c r="D698">
+        <v>4</v>
+      </c>
+      <c r="E698">
+        <v>5</v>
+      </c>
+      <c r="F698">
+        <v>6</v>
+      </c>
+      <c r="G698">
+        <v>7</v>
+      </c>
+      <c r="H698">
+        <v>10</v>
+      </c>
+      <c r="I698">
+        <v>11</v>
+      </c>
+      <c r="J698">
+        <v>12</v>
+      </c>
+      <c r="K698">
+        <v>14</v>
+      </c>
+      <c r="L698">
+        <v>15</v>
+      </c>
+      <c r="M698">
+        <v>17</v>
+      </c>
+      <c r="N698">
+        <v>20</v>
+      </c>
+      <c r="O698">
+        <v>23</v>
+      </c>
+      <c r="P698">
         <v>24</v>
       </c>
     </row>
     <row r="699" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A699" s="5">
+      <c r="A699">
         <v>3769</v>
       </c>
-      <c r="B699" s="6">
-        <v>1</v>
-      </c>
-      <c r="C699" s="6">
-        <v>2</v>
-      </c>
-      <c r="D699" s="6">
-        <v>3</v>
-      </c>
-      <c r="E699" s="6">
-        <v>4</v>
-      </c>
-      <c r="F699" s="6">
-        <v>5</v>
-      </c>
-      <c r="G699" s="6">
-        <v>9</v>
-      </c>
-      <c r="H699" s="6">
-        <v>10</v>
-      </c>
-      <c r="I699" s="6">
-        <v>11</v>
-      </c>
-      <c r="J699" s="6">
-        <v>15</v>
-      </c>
-      <c r="K699" s="6">
-        <v>16</v>
-      </c>
-      <c r="L699" s="6">
-        <v>17</v>
-      </c>
-      <c r="M699" s="6">
-        <v>21</v>
-      </c>
-      <c r="N699" s="6">
-        <v>23</v>
-      </c>
-      <c r="O699" s="6">
-        <v>24</v>
-      </c>
-      <c r="P699" s="6">
+      <c r="B699">
+        <v>1</v>
+      </c>
+      <c r="C699">
+        <v>2</v>
+      </c>
+      <c r="D699">
+        <v>3</v>
+      </c>
+      <c r="E699">
+        <v>4</v>
+      </c>
+      <c r="F699">
+        <v>5</v>
+      </c>
+      <c r="G699">
+        <v>9</v>
+      </c>
+      <c r="H699">
+        <v>10</v>
+      </c>
+      <c r="I699">
+        <v>11</v>
+      </c>
+      <c r="J699">
+        <v>15</v>
+      </c>
+      <c r="K699">
+        <v>16</v>
+      </c>
+      <c r="L699">
+        <v>17</v>
+      </c>
+      <c r="M699">
+        <v>21</v>
+      </c>
+      <c r="N699">
+        <v>23</v>
+      </c>
+      <c r="O699">
+        <v>24</v>
+      </c>
+      <c r="P699">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="700" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A700">
+        <v>3770</v>
+      </c>
+      <c r="B700">
+        <v>1</v>
+      </c>
+      <c r="C700">
+        <v>2</v>
+      </c>
+      <c r="D700">
+        <v>4</v>
+      </c>
+      <c r="E700">
+        <v>7</v>
+      </c>
+      <c r="F700">
+        <v>8</v>
+      </c>
+      <c r="G700">
+        <v>12</v>
+      </c>
+      <c r="H700">
+        <v>13</v>
+      </c>
+      <c r="I700">
+        <v>15</v>
+      </c>
+      <c r="J700">
+        <v>16</v>
+      </c>
+      <c r="K700">
+        <v>17</v>
+      </c>
+      <c r="L700">
+        <v>18</v>
+      </c>
+      <c r="M700">
+        <v>19</v>
+      </c>
+      <c r="N700">
+        <v>23</v>
+      </c>
+      <c r="O700">
+        <v>24</v>
+      </c>
+      <c r="P700">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="701" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A701">
+        <v>3771</v>
+      </c>
+      <c r="B701">
+        <v>2</v>
+      </c>
+      <c r="C701">
+        <v>3</v>
+      </c>
+      <c r="D701">
+        <v>4</v>
+      </c>
+      <c r="E701">
+        <v>5</v>
+      </c>
+      <c r="F701">
+        <v>9</v>
+      </c>
+      <c r="G701">
+        <v>10</v>
+      </c>
+      <c r="H701">
+        <v>11</v>
+      </c>
+      <c r="I701">
+        <v>12</v>
+      </c>
+      <c r="J701">
+        <v>15</v>
+      </c>
+      <c r="K701">
+        <v>16</v>
+      </c>
+      <c r="L701">
+        <v>17</v>
+      </c>
+      <c r="M701">
+        <v>18</v>
+      </c>
+      <c r="N701">
+        <v>21</v>
+      </c>
+      <c r="O701">
+        <v>23</v>
+      </c>
+      <c r="P701">
         <v>25</v>
       </c>
     </row>
@@ -35443,16 +35541,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -35620,6 +35708,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -35630,17 +35728,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -35660,6 +35747,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B11CFC0-75A3-46B4-A9C3-EAB491A26E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8287C208-3274-4201-9F32-72CDA888443D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60300" yWindow="6345" windowWidth="24705" windowHeight="9000" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="71835" yWindow="465" windowWidth="14565" windowHeight="13800" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P701"/>
+  <dimension ref="A1:P703"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -35535,12 +35535,122 @@
         <v>25</v>
       </c>
     </row>
+    <row r="702" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A702">
+        <v>3772</v>
+      </c>
+      <c r="B702">
+        <v>3</v>
+      </c>
+      <c r="C702">
+        <v>5</v>
+      </c>
+      <c r="D702">
+        <v>6</v>
+      </c>
+      <c r="E702">
+        <v>7</v>
+      </c>
+      <c r="F702">
+        <v>8</v>
+      </c>
+      <c r="G702">
+        <v>9</v>
+      </c>
+      <c r="H702">
+        <v>11</v>
+      </c>
+      <c r="I702">
+        <v>12</v>
+      </c>
+      <c r="J702">
+        <v>14</v>
+      </c>
+      <c r="K702">
+        <v>15</v>
+      </c>
+      <c r="L702">
+        <v>18</v>
+      </c>
+      <c r="M702">
+        <v>20</v>
+      </c>
+      <c r="N702">
+        <v>21</v>
+      </c>
+      <c r="O702">
+        <v>23</v>
+      </c>
+      <c r="P702">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="703" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A703">
+        <v>3773</v>
+      </c>
+      <c r="B703">
+        <v>3</v>
+      </c>
+      <c r="C703">
+        <v>4</v>
+      </c>
+      <c r="D703">
+        <v>7</v>
+      </c>
+      <c r="E703">
+        <v>9</v>
+      </c>
+      <c r="F703">
+        <v>11</v>
+      </c>
+      <c r="G703">
+        <v>13</v>
+      </c>
+      <c r="H703">
+        <v>14</v>
+      </c>
+      <c r="I703">
+        <v>15</v>
+      </c>
+      <c r="J703">
+        <v>17</v>
+      </c>
+      <c r="K703">
+        <v>18</v>
+      </c>
+      <c r="L703">
+        <v>20</v>
+      </c>
+      <c r="M703">
+        <v>21</v>
+      </c>
+      <c r="N703">
+        <v>22</v>
+      </c>
+      <c r="O703">
+        <v>24</v>
+      </c>
+      <c r="P703">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -35708,16 +35818,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -35728,6 +35828,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -35747,17 +35858,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8287C208-3274-4201-9F32-72CDA888443D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36D9797-5431-453E-81AF-026672CE9798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="71835" yWindow="465" windowWidth="14565" windowHeight="13800" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P703"/>
+  <dimension ref="A1:P704"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -35635,22 +35635,62 @@
         <v>25</v>
       </c>
     </row>
+    <row r="704" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A704">
+        <v>3774</v>
+      </c>
+      <c r="B704">
+        <v>1</v>
+      </c>
+      <c r="C704">
+        <v>3</v>
+      </c>
+      <c r="D704">
+        <v>4</v>
+      </c>
+      <c r="E704">
+        <v>5</v>
+      </c>
+      <c r="F704">
+        <v>6</v>
+      </c>
+      <c r="G704">
+        <v>7</v>
+      </c>
+      <c r="H704">
+        <v>9</v>
+      </c>
+      <c r="I704">
+        <v>12</v>
+      </c>
+      <c r="J704">
+        <v>14</v>
+      </c>
+      <c r="K704">
+        <v>15</v>
+      </c>
+      <c r="L704">
+        <v>16</v>
+      </c>
+      <c r="M704">
+        <v>18</v>
+      </c>
+      <c r="N704">
+        <v>19</v>
+      </c>
+      <c r="O704">
+        <v>23</v>
+      </c>
+      <c r="P704">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -35818,6 +35858,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -35828,17 +35878,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -35858,6 +35897,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36D9797-5431-453E-81AF-026672CE9798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D123657-8425-478D-92AC-230DF012443E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71835" yWindow="465" windowWidth="14565" windowHeight="13800" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="59100" yWindow="435" windowWidth="26715" windowHeight="7815" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -148,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -156,6 +156,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -476,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P704"/>
+  <dimension ref="A1:P709"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -35685,12 +35687,272 @@
         <v>24</v>
       </c>
     </row>
+    <row r="705" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A705" s="5">
+        <v>3775</v>
+      </c>
+      <c r="B705" s="6">
+        <v>1</v>
+      </c>
+      <c r="C705" s="6">
+        <v>4</v>
+      </c>
+      <c r="D705" s="6">
+        <v>5</v>
+      </c>
+      <c r="E705" s="6">
+        <v>6</v>
+      </c>
+      <c r="F705" s="6">
+        <v>8</v>
+      </c>
+      <c r="G705" s="6">
+        <v>10</v>
+      </c>
+      <c r="H705" s="6">
+        <v>11</v>
+      </c>
+      <c r="I705" s="6">
+        <v>12</v>
+      </c>
+      <c r="J705" s="6">
+        <v>13</v>
+      </c>
+      <c r="K705" s="6">
+        <v>15</v>
+      </c>
+      <c r="L705" s="6">
+        <v>17</v>
+      </c>
+      <c r="M705" s="6">
+        <v>18</v>
+      </c>
+      <c r="N705" s="6">
+        <v>19</v>
+      </c>
+      <c r="O705" s="6">
+        <v>23</v>
+      </c>
+      <c r="P705" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="706" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A706" s="5">
+        <v>3776</v>
+      </c>
+      <c r="B706" s="6">
+        <v>3</v>
+      </c>
+      <c r="C706" s="6">
+        <v>5</v>
+      </c>
+      <c r="D706" s="6">
+        <v>7</v>
+      </c>
+      <c r="E706" s="6">
+        <v>8</v>
+      </c>
+      <c r="F706" s="6">
+        <v>10</v>
+      </c>
+      <c r="G706" s="6">
+        <v>14</v>
+      </c>
+      <c r="H706" s="6">
+        <v>16</v>
+      </c>
+      <c r="I706" s="6">
+        <v>17</v>
+      </c>
+      <c r="J706" s="6">
+        <v>18</v>
+      </c>
+      <c r="K706" s="6">
+        <v>19</v>
+      </c>
+      <c r="L706" s="6">
+        <v>20</v>
+      </c>
+      <c r="M706" s="6">
+        <v>21</v>
+      </c>
+      <c r="N706" s="6">
+        <v>23</v>
+      </c>
+      <c r="O706" s="6">
+        <v>24</v>
+      </c>
+      <c r="P706" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="707" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A707" s="5">
+        <v>3777</v>
+      </c>
+      <c r="B707" s="6">
+        <v>3</v>
+      </c>
+      <c r="C707" s="6">
+        <v>5</v>
+      </c>
+      <c r="D707" s="6">
+        <v>7</v>
+      </c>
+      <c r="E707" s="6">
+        <v>8</v>
+      </c>
+      <c r="F707" s="6">
+        <v>9</v>
+      </c>
+      <c r="G707" s="6">
+        <v>10</v>
+      </c>
+      <c r="H707" s="6">
+        <v>12</v>
+      </c>
+      <c r="I707" s="6">
+        <v>13</v>
+      </c>
+      <c r="J707" s="6">
+        <v>15</v>
+      </c>
+      <c r="K707" s="6">
+        <v>19</v>
+      </c>
+      <c r="L707" s="6">
+        <v>20</v>
+      </c>
+      <c r="M707" s="6">
+        <v>21</v>
+      </c>
+      <c r="N707" s="6">
+        <v>22</v>
+      </c>
+      <c r="O707" s="6">
+        <v>24</v>
+      </c>
+      <c r="P707" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="708" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A708" s="5">
+        <v>3778</v>
+      </c>
+      <c r="B708" s="6">
+        <v>1</v>
+      </c>
+      <c r="C708" s="6">
+        <v>2</v>
+      </c>
+      <c r="D708" s="6">
+        <v>3</v>
+      </c>
+      <c r="E708" s="6">
+        <v>5</v>
+      </c>
+      <c r="F708" s="6">
+        <v>6</v>
+      </c>
+      <c r="G708" s="6">
+        <v>8</v>
+      </c>
+      <c r="H708" s="6">
+        <v>9</v>
+      </c>
+      <c r="I708" s="6">
+        <v>10</v>
+      </c>
+      <c r="J708" s="6">
+        <v>13</v>
+      </c>
+      <c r="K708" s="6">
+        <v>14</v>
+      </c>
+      <c r="L708" s="6">
+        <v>16</v>
+      </c>
+      <c r="M708" s="6">
+        <v>17</v>
+      </c>
+      <c r="N708" s="6">
+        <v>18</v>
+      </c>
+      <c r="O708" s="6">
+        <v>20</v>
+      </c>
+      <c r="P708" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="709" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A709" s="5">
+        <v>3779</v>
+      </c>
+      <c r="B709" s="6">
+        <v>3</v>
+      </c>
+      <c r="C709" s="6">
+        <v>4</v>
+      </c>
+      <c r="D709" s="6">
+        <v>5</v>
+      </c>
+      <c r="E709" s="6">
+        <v>7</v>
+      </c>
+      <c r="F709" s="6">
+        <v>8</v>
+      </c>
+      <c r="G709" s="6">
+        <v>10</v>
+      </c>
+      <c r="H709" s="6">
+        <v>11</v>
+      </c>
+      <c r="I709" s="6">
+        <v>13</v>
+      </c>
+      <c r="J709" s="6">
+        <v>14</v>
+      </c>
+      <c r="K709" s="6">
+        <v>16</v>
+      </c>
+      <c r="L709" s="6">
+        <v>17</v>
+      </c>
+      <c r="M709" s="6">
+        <v>19</v>
+      </c>
+      <c r="N709" s="6">
+        <v>23</v>
+      </c>
+      <c r="O709" s="6">
+        <v>24</v>
+      </c>
+      <c r="P709" s="6">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -35858,16 +36120,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -35878,6 +36130,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -35897,17 +36160,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D123657-8425-478D-92AC-230DF012443E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E1011E5-7C94-4176-9CAB-ED0253B00963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59100" yWindow="435" windowWidth="26715" windowHeight="7815" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="2175" yWindow="2175" windowWidth="21217" windowHeight="11490" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -478,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P709"/>
+  <dimension ref="A1:P720"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -35688,252 +35688,802 @@
       </c>
     </row>
     <row r="705" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A705" s="5">
+      <c r="A705">
         <v>3775</v>
       </c>
-      <c r="B705" s="6">
-        <v>1</v>
-      </c>
-      <c r="C705" s="6">
-        <v>4</v>
-      </c>
-      <c r="D705" s="6">
-        <v>5</v>
-      </c>
-      <c r="E705" s="6">
-        <v>6</v>
-      </c>
-      <c r="F705" s="6">
-        <v>8</v>
-      </c>
-      <c r="G705" s="6">
-        <v>10</v>
-      </c>
-      <c r="H705" s="6">
-        <v>11</v>
-      </c>
-      <c r="I705" s="6">
-        <v>12</v>
-      </c>
-      <c r="J705" s="6">
-        <v>13</v>
-      </c>
-      <c r="K705" s="6">
-        <v>15</v>
-      </c>
-      <c r="L705" s="6">
-        <v>17</v>
-      </c>
-      <c r="M705" s="6">
-        <v>18</v>
-      </c>
-      <c r="N705" s="6">
-        <v>19</v>
-      </c>
-      <c r="O705" s="6">
-        <v>23</v>
-      </c>
-      <c r="P705" s="6">
+      <c r="B705">
+        <v>1</v>
+      </c>
+      <c r="C705">
+        <v>4</v>
+      </c>
+      <c r="D705">
+        <v>5</v>
+      </c>
+      <c r="E705">
+        <v>6</v>
+      </c>
+      <c r="F705">
+        <v>8</v>
+      </c>
+      <c r="G705">
+        <v>10</v>
+      </c>
+      <c r="H705">
+        <v>11</v>
+      </c>
+      <c r="I705">
+        <v>12</v>
+      </c>
+      <c r="J705">
+        <v>13</v>
+      </c>
+      <c r="K705">
+        <v>15</v>
+      </c>
+      <c r="L705">
+        <v>17</v>
+      </c>
+      <c r="M705">
+        <v>18</v>
+      </c>
+      <c r="N705">
+        <v>19</v>
+      </c>
+      <c r="O705">
+        <v>23</v>
+      </c>
+      <c r="P705">
         <v>25</v>
       </c>
     </row>
     <row r="706" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A706" s="5">
+      <c r="A706">
         <v>3776</v>
       </c>
-      <c r="B706" s="6">
-        <v>3</v>
-      </c>
-      <c r="C706" s="6">
-        <v>5</v>
-      </c>
-      <c r="D706" s="6">
-        <v>7</v>
-      </c>
-      <c r="E706" s="6">
-        <v>8</v>
-      </c>
-      <c r="F706" s="6">
-        <v>10</v>
-      </c>
-      <c r="G706" s="6">
-        <v>14</v>
-      </c>
-      <c r="H706" s="6">
-        <v>16</v>
-      </c>
-      <c r="I706" s="6">
-        <v>17</v>
-      </c>
-      <c r="J706" s="6">
-        <v>18</v>
-      </c>
-      <c r="K706" s="6">
-        <v>19</v>
-      </c>
-      <c r="L706" s="6">
-        <v>20</v>
-      </c>
-      <c r="M706" s="6">
-        <v>21</v>
-      </c>
-      <c r="N706" s="6">
-        <v>23</v>
-      </c>
-      <c r="O706" s="6">
-        <v>24</v>
-      </c>
-      <c r="P706" s="6">
+      <c r="B706">
+        <v>3</v>
+      </c>
+      <c r="C706">
+        <v>5</v>
+      </c>
+      <c r="D706">
+        <v>7</v>
+      </c>
+      <c r="E706">
+        <v>8</v>
+      </c>
+      <c r="F706">
+        <v>10</v>
+      </c>
+      <c r="G706">
+        <v>14</v>
+      </c>
+      <c r="H706">
+        <v>16</v>
+      </c>
+      <c r="I706">
+        <v>17</v>
+      </c>
+      <c r="J706">
+        <v>18</v>
+      </c>
+      <c r="K706">
+        <v>19</v>
+      </c>
+      <c r="L706">
+        <v>20</v>
+      </c>
+      <c r="M706">
+        <v>21</v>
+      </c>
+      <c r="N706">
+        <v>23</v>
+      </c>
+      <c r="O706">
+        <v>24</v>
+      </c>
+      <c r="P706">
         <v>25</v>
       </c>
     </row>
     <row r="707" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A707" s="5">
+      <c r="A707">
         <v>3777</v>
       </c>
-      <c r="B707" s="6">
-        <v>3</v>
-      </c>
-      <c r="C707" s="6">
-        <v>5</v>
-      </c>
-      <c r="D707" s="6">
-        <v>7</v>
-      </c>
-      <c r="E707" s="6">
-        <v>8</v>
-      </c>
-      <c r="F707" s="6">
-        <v>9</v>
-      </c>
-      <c r="G707" s="6">
-        <v>10</v>
-      </c>
-      <c r="H707" s="6">
-        <v>12</v>
-      </c>
-      <c r="I707" s="6">
-        <v>13</v>
-      </c>
-      <c r="J707" s="6">
-        <v>15</v>
-      </c>
-      <c r="K707" s="6">
-        <v>19</v>
-      </c>
-      <c r="L707" s="6">
-        <v>20</v>
-      </c>
-      <c r="M707" s="6">
-        <v>21</v>
-      </c>
-      <c r="N707" s="6">
-        <v>22</v>
-      </c>
-      <c r="O707" s="6">
-        <v>24</v>
-      </c>
-      <c r="P707" s="6">
+      <c r="B707">
+        <v>3</v>
+      </c>
+      <c r="C707">
+        <v>5</v>
+      </c>
+      <c r="D707">
+        <v>7</v>
+      </c>
+      <c r="E707">
+        <v>8</v>
+      </c>
+      <c r="F707">
+        <v>9</v>
+      </c>
+      <c r="G707">
+        <v>10</v>
+      </c>
+      <c r="H707">
+        <v>12</v>
+      </c>
+      <c r="I707">
+        <v>13</v>
+      </c>
+      <c r="J707">
+        <v>15</v>
+      </c>
+      <c r="K707">
+        <v>19</v>
+      </c>
+      <c r="L707">
+        <v>20</v>
+      </c>
+      <c r="M707">
+        <v>21</v>
+      </c>
+      <c r="N707">
+        <v>22</v>
+      </c>
+      <c r="O707">
+        <v>24</v>
+      </c>
+      <c r="P707">
         <v>25</v>
       </c>
     </row>
     <row r="708" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A708" s="5">
+      <c r="A708">
         <v>3778</v>
       </c>
-      <c r="B708" s="6">
-        <v>1</v>
-      </c>
-      <c r="C708" s="6">
-        <v>2</v>
-      </c>
-      <c r="D708" s="6">
-        <v>3</v>
-      </c>
-      <c r="E708" s="6">
-        <v>5</v>
-      </c>
-      <c r="F708" s="6">
-        <v>6</v>
-      </c>
-      <c r="G708" s="6">
-        <v>8</v>
-      </c>
-      <c r="H708" s="6">
-        <v>9</v>
-      </c>
-      <c r="I708" s="6">
-        <v>10</v>
-      </c>
-      <c r="J708" s="6">
-        <v>13</v>
-      </c>
-      <c r="K708" s="6">
-        <v>14</v>
-      </c>
-      <c r="L708" s="6">
-        <v>16</v>
-      </c>
-      <c r="M708" s="6">
-        <v>17</v>
-      </c>
-      <c r="N708" s="6">
-        <v>18</v>
-      </c>
-      <c r="O708" s="6">
-        <v>20</v>
-      </c>
-      <c r="P708" s="6">
+      <c r="B708">
+        <v>1</v>
+      </c>
+      <c r="C708">
+        <v>2</v>
+      </c>
+      <c r="D708">
+        <v>3</v>
+      </c>
+      <c r="E708">
+        <v>5</v>
+      </c>
+      <c r="F708">
+        <v>6</v>
+      </c>
+      <c r="G708">
+        <v>8</v>
+      </c>
+      <c r="H708">
+        <v>9</v>
+      </c>
+      <c r="I708">
+        <v>10</v>
+      </c>
+      <c r="J708">
+        <v>13</v>
+      </c>
+      <c r="K708">
+        <v>14</v>
+      </c>
+      <c r="L708">
+        <v>16</v>
+      </c>
+      <c r="M708">
+        <v>17</v>
+      </c>
+      <c r="N708">
+        <v>18</v>
+      </c>
+      <c r="O708">
+        <v>20</v>
+      </c>
+      <c r="P708">
         <v>22</v>
       </c>
     </row>
     <row r="709" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A709" s="5">
+      <c r="A709">
         <v>3779</v>
       </c>
-      <c r="B709" s="6">
-        <v>3</v>
-      </c>
-      <c r="C709" s="6">
-        <v>4</v>
-      </c>
-      <c r="D709" s="6">
-        <v>5</v>
-      </c>
-      <c r="E709" s="6">
-        <v>7</v>
-      </c>
-      <c r="F709" s="6">
-        <v>8</v>
-      </c>
-      <c r="G709" s="6">
-        <v>10</v>
-      </c>
-      <c r="H709" s="6">
-        <v>11</v>
-      </c>
-      <c r="I709" s="6">
-        <v>13</v>
-      </c>
-      <c r="J709" s="6">
-        <v>14</v>
-      </c>
-      <c r="K709" s="6">
-        <v>16</v>
-      </c>
-      <c r="L709" s="6">
-        <v>17</v>
-      </c>
-      <c r="M709" s="6">
-        <v>19</v>
-      </c>
-      <c r="N709" s="6">
-        <v>23</v>
-      </c>
-      <c r="O709" s="6">
-        <v>24</v>
-      </c>
-      <c r="P709" s="6">
+      <c r="B709">
+        <v>3</v>
+      </c>
+      <c r="C709">
+        <v>4</v>
+      </c>
+      <c r="D709">
+        <v>5</v>
+      </c>
+      <c r="E709">
+        <v>7</v>
+      </c>
+      <c r="F709">
+        <v>8</v>
+      </c>
+      <c r="G709">
+        <v>10</v>
+      </c>
+      <c r="H709">
+        <v>11</v>
+      </c>
+      <c r="I709">
+        <v>13</v>
+      </c>
+      <c r="J709">
+        <v>14</v>
+      </c>
+      <c r="K709">
+        <v>16</v>
+      </c>
+      <c r="L709">
+        <v>17</v>
+      </c>
+      <c r="M709">
+        <v>19</v>
+      </c>
+      <c r="N709">
+        <v>23</v>
+      </c>
+      <c r="O709">
+        <v>24</v>
+      </c>
+      <c r="P709">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="710" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A710" s="5">
+        <v>3780</v>
+      </c>
+      <c r="B710" s="6">
+        <v>1</v>
+      </c>
+      <c r="C710" s="6">
+        <v>2</v>
+      </c>
+      <c r="D710" s="6">
+        <v>3</v>
+      </c>
+      <c r="E710" s="6">
+        <v>4</v>
+      </c>
+      <c r="F710" s="6">
+        <v>5</v>
+      </c>
+      <c r="G710" s="6">
+        <v>6</v>
+      </c>
+      <c r="H710" s="6">
+        <v>7</v>
+      </c>
+      <c r="I710" s="6">
+        <v>12</v>
+      </c>
+      <c r="J710" s="6">
+        <v>15</v>
+      </c>
+      <c r="K710" s="6">
+        <v>16</v>
+      </c>
+      <c r="L710" s="6">
+        <v>17</v>
+      </c>
+      <c r="M710" s="6">
+        <v>19</v>
+      </c>
+      <c r="N710" s="6">
+        <v>21</v>
+      </c>
+      <c r="O710" s="6">
+        <v>22</v>
+      </c>
+      <c r="P710" s="6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="711" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A711" s="5">
+        <v>3781</v>
+      </c>
+      <c r="B711" s="6">
+        <v>3</v>
+      </c>
+      <c r="C711" s="6">
+        <v>5</v>
+      </c>
+      <c r="D711" s="6">
+        <v>6</v>
+      </c>
+      <c r="E711" s="6">
+        <v>7</v>
+      </c>
+      <c r="F711" s="6">
+        <v>8</v>
+      </c>
+      <c r="G711" s="6">
+        <v>9</v>
+      </c>
+      <c r="H711" s="6">
+        <v>11</v>
+      </c>
+      <c r="I711" s="6">
+        <v>12</v>
+      </c>
+      <c r="J711" s="6">
+        <v>13</v>
+      </c>
+      <c r="K711" s="6">
+        <v>16</v>
+      </c>
+      <c r="L711" s="6">
+        <v>19</v>
+      </c>
+      <c r="M711" s="6">
+        <v>21</v>
+      </c>
+      <c r="N711" s="6">
+        <v>22</v>
+      </c>
+      <c r="O711" s="6">
+        <v>24</v>
+      </c>
+      <c r="P711" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="712" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A712" s="5">
+        <v>3782</v>
+      </c>
+      <c r="B712" s="6">
+        <v>3</v>
+      </c>
+      <c r="C712" s="6">
+        <v>4</v>
+      </c>
+      <c r="D712" s="6">
+        <v>5</v>
+      </c>
+      <c r="E712" s="6">
+        <v>7</v>
+      </c>
+      <c r="F712" s="6">
+        <v>8</v>
+      </c>
+      <c r="G712" s="6">
+        <v>11</v>
+      </c>
+      <c r="H712" s="6">
+        <v>15</v>
+      </c>
+      <c r="I712" s="6">
+        <v>16</v>
+      </c>
+      <c r="J712" s="6">
+        <v>17</v>
+      </c>
+      <c r="K712" s="6">
+        <v>18</v>
+      </c>
+      <c r="L712" s="6">
+        <v>19</v>
+      </c>
+      <c r="M712" s="6">
+        <v>20</v>
+      </c>
+      <c r="N712" s="6">
+        <v>22</v>
+      </c>
+      <c r="O712" s="6">
+        <v>23</v>
+      </c>
+      <c r="P712" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="713" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A713" s="5">
+        <v>3783</v>
+      </c>
+      <c r="B713" s="6">
+        <v>1</v>
+      </c>
+      <c r="C713" s="6">
+        <v>3</v>
+      </c>
+      <c r="D713" s="6">
+        <v>4</v>
+      </c>
+      <c r="E713" s="6">
+        <v>5</v>
+      </c>
+      <c r="F713" s="6">
+        <v>6</v>
+      </c>
+      <c r="G713" s="6">
+        <v>12</v>
+      </c>
+      <c r="H713" s="6">
+        <v>14</v>
+      </c>
+      <c r="I713" s="6">
+        <v>15</v>
+      </c>
+      <c r="J713" s="6">
+        <v>16</v>
+      </c>
+      <c r="K713" s="6">
+        <v>17</v>
+      </c>
+      <c r="L713" s="6">
+        <v>19</v>
+      </c>
+      <c r="M713" s="6">
+        <v>22</v>
+      </c>
+      <c r="N713" s="6">
+        <v>23</v>
+      </c>
+      <c r="O713" s="6">
+        <v>24</v>
+      </c>
+      <c r="P713" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="714" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A714" s="5">
+        <v>3784</v>
+      </c>
+      <c r="B714" s="6">
+        <v>1</v>
+      </c>
+      <c r="C714" s="6">
+        <v>2</v>
+      </c>
+      <c r="D714" s="6">
+        <v>8</v>
+      </c>
+      <c r="E714" s="6">
+        <v>10</v>
+      </c>
+      <c r="F714" s="6">
+        <v>11</v>
+      </c>
+      <c r="G714" s="6">
+        <v>12</v>
+      </c>
+      <c r="H714" s="6">
+        <v>15</v>
+      </c>
+      <c r="I714" s="6">
+        <v>16</v>
+      </c>
+      <c r="J714" s="6">
+        <v>18</v>
+      </c>
+      <c r="K714" s="6">
+        <v>19</v>
+      </c>
+      <c r="L714" s="6">
+        <v>20</v>
+      </c>
+      <c r="M714" s="6">
+        <v>21</v>
+      </c>
+      <c r="N714" s="6">
+        <v>22</v>
+      </c>
+      <c r="O714" s="6">
+        <v>24</v>
+      </c>
+      <c r="P714" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="715" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A715" s="5">
+        <v>3785</v>
+      </c>
+      <c r="B715" s="6">
+        <v>1</v>
+      </c>
+      <c r="C715" s="6">
+        <v>4</v>
+      </c>
+      <c r="D715" s="6">
+        <v>7</v>
+      </c>
+      <c r="E715" s="6">
+        <v>8</v>
+      </c>
+      <c r="F715" s="6">
+        <v>11</v>
+      </c>
+      <c r="G715" s="6">
+        <v>12</v>
+      </c>
+      <c r="H715" s="6">
+        <v>14</v>
+      </c>
+      <c r="I715" s="6">
+        <v>15</v>
+      </c>
+      <c r="J715" s="6">
+        <v>17</v>
+      </c>
+      <c r="K715" s="6">
+        <v>18</v>
+      </c>
+      <c r="L715" s="6">
+        <v>19</v>
+      </c>
+      <c r="M715" s="6">
+        <v>22</v>
+      </c>
+      <c r="N715" s="6">
+        <v>23</v>
+      </c>
+      <c r="O715" s="6">
+        <v>24</v>
+      </c>
+      <c r="P715" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="716" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A716" s="5">
+        <v>3786</v>
+      </c>
+      <c r="B716" s="6">
+        <v>1</v>
+      </c>
+      <c r="C716" s="6">
+        <v>3</v>
+      </c>
+      <c r="D716" s="6">
+        <v>6</v>
+      </c>
+      <c r="E716" s="6">
+        <v>7</v>
+      </c>
+      <c r="F716" s="6">
+        <v>8</v>
+      </c>
+      <c r="G716" s="6">
+        <v>9</v>
+      </c>
+      <c r="H716" s="6">
+        <v>12</v>
+      </c>
+      <c r="I716" s="6">
+        <v>13</v>
+      </c>
+      <c r="J716" s="6">
+        <v>14</v>
+      </c>
+      <c r="K716" s="6">
+        <v>16</v>
+      </c>
+      <c r="L716" s="6">
+        <v>18</v>
+      </c>
+      <c r="M716" s="6">
+        <v>21</v>
+      </c>
+      <c r="N716" s="6">
+        <v>23</v>
+      </c>
+      <c r="O716" s="6">
+        <v>24</v>
+      </c>
+      <c r="P716" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="717" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A717" s="5">
+        <v>3787</v>
+      </c>
+      <c r="B717" s="6">
+        <v>3</v>
+      </c>
+      <c r="C717" s="6">
+        <v>4</v>
+      </c>
+      <c r="D717" s="6">
+        <v>6</v>
+      </c>
+      <c r="E717" s="6">
+        <v>8</v>
+      </c>
+      <c r="F717" s="6">
+        <v>10</v>
+      </c>
+      <c r="G717" s="6">
+        <v>11</v>
+      </c>
+      <c r="H717" s="6">
+        <v>12</v>
+      </c>
+      <c r="I717" s="6">
+        <v>13</v>
+      </c>
+      <c r="J717" s="6">
+        <v>15</v>
+      </c>
+      <c r="K717" s="6">
+        <v>17</v>
+      </c>
+      <c r="L717" s="6">
+        <v>19</v>
+      </c>
+      <c r="M717" s="6">
+        <v>20</v>
+      </c>
+      <c r="N717" s="6">
+        <v>22</v>
+      </c>
+      <c r="O717" s="6">
+        <v>23</v>
+      </c>
+      <c r="P717" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="718" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A718" s="5">
+        <v>3788</v>
+      </c>
+      <c r="B718" s="6">
+        <v>1</v>
+      </c>
+      <c r="C718" s="6">
+        <v>4</v>
+      </c>
+      <c r="D718" s="6">
+        <v>5</v>
+      </c>
+      <c r="E718" s="6">
+        <v>7</v>
+      </c>
+      <c r="F718" s="6">
+        <v>8</v>
+      </c>
+      <c r="G718" s="6">
+        <v>9</v>
+      </c>
+      <c r="H718" s="6">
+        <v>12</v>
+      </c>
+      <c r="I718" s="6">
+        <v>16</v>
+      </c>
+      <c r="J718" s="6">
+        <v>17</v>
+      </c>
+      <c r="K718" s="6">
+        <v>18</v>
+      </c>
+      <c r="L718" s="6">
+        <v>20</v>
+      </c>
+      <c r="M718" s="6">
+        <v>21</v>
+      </c>
+      <c r="N718" s="6">
+        <v>22</v>
+      </c>
+      <c r="O718" s="6">
+        <v>23</v>
+      </c>
+      <c r="P718" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="719" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A719" s="5">
+        <v>3789</v>
+      </c>
+      <c r="B719" s="6">
+        <v>6</v>
+      </c>
+      <c r="C719" s="6">
+        <v>7</v>
+      </c>
+      <c r="D719" s="6">
+        <v>8</v>
+      </c>
+      <c r="E719" s="6">
+        <v>9</v>
+      </c>
+      <c r="F719" s="6">
+        <v>11</v>
+      </c>
+      <c r="G719" s="6">
+        <v>12</v>
+      </c>
+      <c r="H719" s="6">
+        <v>13</v>
+      </c>
+      <c r="I719" s="6">
+        <v>14</v>
+      </c>
+      <c r="J719" s="6">
+        <v>15</v>
+      </c>
+      <c r="K719" s="6">
+        <v>16</v>
+      </c>
+      <c r="L719" s="6">
+        <v>17</v>
+      </c>
+      <c r="M719" s="6">
+        <v>18</v>
+      </c>
+      <c r="N719" s="6">
+        <v>19</v>
+      </c>
+      <c r="O719" s="6">
+        <v>23</v>
+      </c>
+      <c r="P719" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="720" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A720" s="5">
+        <v>3790</v>
+      </c>
+      <c r="B720" s="6">
+        <v>1</v>
+      </c>
+      <c r="C720" s="6">
+        <v>3</v>
+      </c>
+      <c r="D720" s="6">
+        <v>4</v>
+      </c>
+      <c r="E720" s="6">
+        <v>5</v>
+      </c>
+      <c r="F720" s="6">
+        <v>6</v>
+      </c>
+      <c r="G720" s="6">
+        <v>7</v>
+      </c>
+      <c r="H720" s="6">
+        <v>9</v>
+      </c>
+      <c r="I720" s="6">
+        <v>11</v>
+      </c>
+      <c r="J720" s="6">
+        <v>14</v>
+      </c>
+      <c r="K720" s="6">
+        <v>15</v>
+      </c>
+      <c r="L720" s="6">
+        <v>16</v>
+      </c>
+      <c r="M720" s="6">
+        <v>17</v>
+      </c>
+      <c r="N720" s="6">
+        <v>20</v>
+      </c>
+      <c r="O720" s="6">
+        <v>21</v>
+      </c>
+      <c r="P720" s="6">
         <v>25</v>
       </c>
     </row>
@@ -35943,16 +36493,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -36120,6 +36660,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -36130,17 +36680,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -36160,6 +36699,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Lotofacil_edt2.xlsx
+++ b/LoteriasExcel/Lotofacil_edt2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E1011E5-7C94-4176-9CAB-ED0253B00963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA5B273C-5B47-4C53-A439-5FB7C2CCC21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2175" yWindow="2175" windowWidth="21217" windowHeight="11490" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57810" yWindow="45" windowWidth="19845" windowHeight="11865" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="LOTOFÁCIL" sheetId="3" r:id="rId1"/>
@@ -148,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -156,8 +156,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BEFC42-DD13-4DE0-B2AD-D0F44AF8189C}">
-  <dimension ref="A1:P720"/>
+  <dimension ref="A1:P723"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="17" max="17" width="11.6640625" customWidth="1"/>
@@ -35938,552 +35936,702 @@
       </c>
     </row>
     <row r="710" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A710" s="5">
+      <c r="A710">
         <v>3780</v>
       </c>
-      <c r="B710" s="6">
-        <v>1</v>
-      </c>
-      <c r="C710" s="6">
-        <v>2</v>
-      </c>
-      <c r="D710" s="6">
-        <v>3</v>
-      </c>
-      <c r="E710" s="6">
-        <v>4</v>
-      </c>
-      <c r="F710" s="6">
-        <v>5</v>
-      </c>
-      <c r="G710" s="6">
-        <v>6</v>
-      </c>
-      <c r="H710" s="6">
-        <v>7</v>
-      </c>
-      <c r="I710" s="6">
-        <v>12</v>
-      </c>
-      <c r="J710" s="6">
-        <v>15</v>
-      </c>
-      <c r="K710" s="6">
-        <v>16</v>
-      </c>
-      <c r="L710" s="6">
-        <v>17</v>
-      </c>
-      <c r="M710" s="6">
-        <v>19</v>
-      </c>
-      <c r="N710" s="6">
-        <v>21</v>
-      </c>
-      <c r="O710" s="6">
-        <v>22</v>
-      </c>
-      <c r="P710" s="6">
+      <c r="B710">
+        <v>1</v>
+      </c>
+      <c r="C710">
+        <v>2</v>
+      </c>
+      <c r="D710">
+        <v>3</v>
+      </c>
+      <c r="E710">
+        <v>4</v>
+      </c>
+      <c r="F710">
+        <v>5</v>
+      </c>
+      <c r="G710">
+        <v>6</v>
+      </c>
+      <c r="H710">
+        <v>7</v>
+      </c>
+      <c r="I710">
+        <v>12</v>
+      </c>
+      <c r="J710">
+        <v>15</v>
+      </c>
+      <c r="K710">
+        <v>16</v>
+      </c>
+      <c r="L710">
+        <v>17</v>
+      </c>
+      <c r="M710">
+        <v>19</v>
+      </c>
+      <c r="N710">
+        <v>21</v>
+      </c>
+      <c r="O710">
+        <v>22</v>
+      </c>
+      <c r="P710">
         <v>23</v>
       </c>
     </row>
     <row r="711" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A711" s="5">
+      <c r="A711">
         <v>3781</v>
       </c>
-      <c r="B711" s="6">
-        <v>3</v>
-      </c>
-      <c r="C711" s="6">
-        <v>5</v>
-      </c>
-      <c r="D711" s="6">
-        <v>6</v>
-      </c>
-      <c r="E711" s="6">
-        <v>7</v>
-      </c>
-      <c r="F711" s="6">
-        <v>8</v>
-      </c>
-      <c r="G711" s="6">
-        <v>9</v>
-      </c>
-      <c r="H711" s="6">
-        <v>11</v>
-      </c>
-      <c r="I711" s="6">
-        <v>12</v>
-      </c>
-      <c r="J711" s="6">
-        <v>13</v>
-      </c>
-      <c r="K711" s="6">
-        <v>16</v>
-      </c>
-      <c r="L711" s="6">
-        <v>19</v>
-      </c>
-      <c r="M711" s="6">
-        <v>21</v>
-      </c>
-      <c r="N711" s="6">
-        <v>22</v>
-      </c>
-      <c r="O711" s="6">
-        <v>24</v>
-      </c>
-      <c r="P711" s="6">
+      <c r="B711">
+        <v>3</v>
+      </c>
+      <c r="C711">
+        <v>5</v>
+      </c>
+      <c r="D711">
+        <v>6</v>
+      </c>
+      <c r="E711">
+        <v>7</v>
+      </c>
+      <c r="F711">
+        <v>8</v>
+      </c>
+      <c r="G711">
+        <v>9</v>
+      </c>
+      <c r="H711">
+        <v>11</v>
+      </c>
+      <c r="I711">
+        <v>12</v>
+      </c>
+      <c r="J711">
+        <v>13</v>
+      </c>
+      <c r="K711">
+        <v>16</v>
+      </c>
+      <c r="L711">
+        <v>19</v>
+      </c>
+      <c r="M711">
+        <v>21</v>
+      </c>
+      <c r="N711">
+        <v>22</v>
+      </c>
+      <c r="O711">
+        <v>24</v>
+      </c>
+      <c r="P711">
         <v>25</v>
       </c>
     </row>
     <row r="712" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A712" s="5">
+      <c r="A712">
         <v>3782</v>
       </c>
-      <c r="B712" s="6">
-        <v>3</v>
-      </c>
-      <c r="C712" s="6">
-        <v>4</v>
-      </c>
-      <c r="D712" s="6">
-        <v>5</v>
-      </c>
-      <c r="E712" s="6">
-        <v>7</v>
-      </c>
-      <c r="F712" s="6">
-        <v>8</v>
-      </c>
-      <c r="G712" s="6">
-        <v>11</v>
-      </c>
-      <c r="H712" s="6">
-        <v>15</v>
-      </c>
-      <c r="I712" s="6">
-        <v>16</v>
-      </c>
-      <c r="J712" s="6">
-        <v>17</v>
-      </c>
-      <c r="K712" s="6">
-        <v>18</v>
-      </c>
-      <c r="L712" s="6">
-        <v>19</v>
-      </c>
-      <c r="M712" s="6">
-        <v>20</v>
-      </c>
-      <c r="N712" s="6">
-        <v>22</v>
-      </c>
-      <c r="O712" s="6">
-        <v>23</v>
-      </c>
-      <c r="P712" s="6">
+      <c r="B712">
+        <v>3</v>
+      </c>
+      <c r="C712">
+        <v>4</v>
+      </c>
+      <c r="D712">
+        <v>5</v>
+      </c>
+      <c r="E712">
+        <v>7</v>
+      </c>
+      <c r="F712">
+        <v>8</v>
+      </c>
+      <c r="G712">
+        <v>11</v>
+      </c>
+      <c r="H712">
+        <v>15</v>
+      </c>
+      <c r="I712">
+        <v>16</v>
+      </c>
+      <c r="J712">
+        <v>17</v>
+      </c>
+      <c r="K712">
+        <v>18</v>
+      </c>
+      <c r="L712">
+        <v>19</v>
+      </c>
+      <c r="M712">
+        <v>20</v>
+      </c>
+      <c r="N712">
+        <v>22</v>
+      </c>
+      <c r="O712">
+        <v>23</v>
+      </c>
+      <c r="P712">
         <v>25</v>
       </c>
     </row>
     <row r="713" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A713" s="5">
+      <c r="A713">
         <v>3783</v>
       </c>
-      <c r="B713" s="6">
-        <v>1</v>
-      </c>
-      <c r="C713" s="6">
-        <v>3</v>
-      </c>
-      <c r="D713" s="6">
-        <v>4</v>
-      </c>
-      <c r="E713" s="6">
-        <v>5</v>
-      </c>
-      <c r="F713" s="6">
-        <v>6</v>
-      </c>
-      <c r="G713" s="6">
-        <v>12</v>
-      </c>
-      <c r="H713" s="6">
-        <v>14</v>
-      </c>
-      <c r="I713" s="6">
-        <v>15</v>
-      </c>
-      <c r="J713" s="6">
-        <v>16</v>
-      </c>
-      <c r="K713" s="6">
-        <v>17</v>
-      </c>
-      <c r="L713" s="6">
-        <v>19</v>
-      </c>
-      <c r="M713" s="6">
-        <v>22</v>
-      </c>
-      <c r="N713" s="6">
-        <v>23</v>
-      </c>
-      <c r="O713" s="6">
-        <v>24</v>
-      </c>
-      <c r="P713" s="6">
+      <c r="B713">
+        <v>1</v>
+      </c>
+      <c r="C713">
+        <v>3</v>
+      </c>
+      <c r="D713">
+        <v>4</v>
+      </c>
+      <c r="E713">
+        <v>5</v>
+      </c>
+      <c r="F713">
+        <v>6</v>
+      </c>
+      <c r="G713">
+        <v>12</v>
+      </c>
+      <c r="H713">
+        <v>14</v>
+      </c>
+      <c r="I713">
+        <v>15</v>
+      </c>
+      <c r="J713">
+        <v>16</v>
+      </c>
+      <c r="K713">
+        <v>17</v>
+      </c>
+      <c r="L713">
+        <v>19</v>
+      </c>
+      <c r="M713">
+        <v>22</v>
+      </c>
+      <c r="N713">
+        <v>23</v>
+      </c>
+      <c r="O713">
+        <v>24</v>
+      </c>
+      <c r="P713">
         <v>25</v>
       </c>
     </row>
     <row r="714" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A714" s="5">
+      <c r="A714">
         <v>3784</v>
       </c>
-      <c r="B714" s="6">
-        <v>1</v>
-      </c>
-      <c r="C714" s="6">
-        <v>2</v>
-      </c>
-      <c r="D714" s="6">
-        <v>8</v>
-      </c>
-      <c r="E714" s="6">
-        <v>10</v>
-      </c>
-      <c r="F714" s="6">
-        <v>11</v>
-      </c>
-      <c r="G714" s="6">
-        <v>12</v>
-      </c>
-      <c r="H714" s="6">
-        <v>15</v>
-      </c>
-      <c r="I714" s="6">
-        <v>16</v>
-      </c>
-      <c r="J714" s="6">
-        <v>18</v>
-      </c>
-      <c r="K714" s="6">
-        <v>19</v>
-      </c>
-      <c r="L714" s="6">
-        <v>20</v>
-      </c>
-      <c r="M714" s="6">
-        <v>21</v>
-      </c>
-      <c r="N714" s="6">
-        <v>22</v>
-      </c>
-      <c r="O714" s="6">
-        <v>24</v>
-      </c>
-      <c r="P714" s="6">
+      <c r="B714">
+        <v>1</v>
+      </c>
+      <c r="C714">
+        <v>2</v>
+      </c>
+      <c r="D714">
+        <v>8</v>
+      </c>
+      <c r="E714">
+        <v>10</v>
+      </c>
+      <c r="F714">
+        <v>11</v>
+      </c>
+      <c r="G714">
+        <v>12</v>
+      </c>
+      <c r="H714">
+        <v>15</v>
+      </c>
+      <c r="I714">
+        <v>16</v>
+      </c>
+      <c r="J714">
+        <v>18</v>
+      </c>
+      <c r="K714">
+        <v>19</v>
+      </c>
+      <c r="L714">
+        <v>20</v>
+      </c>
+      <c r="M714">
+        <v>21</v>
+      </c>
+      <c r="N714">
+        <v>22</v>
+      </c>
+      <c r="O714">
+        <v>24</v>
+      </c>
+      <c r="P714">
         <v>25</v>
       </c>
     </row>
     <row r="715" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A715" s="5">
+      <c r="A715">
         <v>3785</v>
       </c>
-      <c r="B715" s="6">
-        <v>1</v>
-      </c>
-      <c r="C715" s="6">
-        <v>4</v>
-      </c>
-      <c r="D715" s="6">
-        <v>7</v>
-      </c>
-      <c r="E715" s="6">
-        <v>8</v>
-      </c>
-      <c r="F715" s="6">
-        <v>11</v>
-      </c>
-      <c r="G715" s="6">
-        <v>12</v>
-      </c>
-      <c r="H715" s="6">
-        <v>14</v>
-      </c>
-      <c r="I715" s="6">
-        <v>15</v>
-      </c>
-      <c r="J715" s="6">
-        <v>17</v>
-      </c>
-      <c r="K715" s="6">
-        <v>18</v>
-      </c>
-      <c r="L715" s="6">
-        <v>19</v>
-      </c>
-      <c r="M715" s="6">
-        <v>22</v>
-      </c>
-      <c r="N715" s="6">
-        <v>23</v>
-      </c>
-      <c r="O715" s="6">
-        <v>24</v>
-      </c>
-      <c r="P715" s="6">
+      <c r="B715">
+        <v>1</v>
+      </c>
+      <c r="C715">
+        <v>4</v>
+      </c>
+      <c r="D715">
+        <v>7</v>
+      </c>
+      <c r="E715">
+        <v>8</v>
+      </c>
+      <c r="F715">
+        <v>11</v>
+      </c>
+      <c r="G715">
+        <v>12</v>
+      </c>
+      <c r="H715">
+        <v>14</v>
+      </c>
+      <c r="I715">
+        <v>15</v>
+      </c>
+      <c r="J715">
+        <v>17</v>
+      </c>
+      <c r="K715">
+        <v>18</v>
+      </c>
+      <c r="L715">
+        <v>19</v>
+      </c>
+      <c r="M715">
+        <v>22</v>
+      </c>
+      <c r="N715">
+        <v>23</v>
+      </c>
+      <c r="O715">
+        <v>24</v>
+      </c>
+      <c r="P715">
         <v>25</v>
       </c>
     </row>
     <row r="716" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A716" s="5">
+      <c r="A716">
         <v>3786</v>
       </c>
-      <c r="B716" s="6">
-        <v>1</v>
-      </c>
-      <c r="C716" s="6">
-        <v>3</v>
-      </c>
-      <c r="D716" s="6">
-        <v>6</v>
-      </c>
-      <c r="E716" s="6">
-        <v>7</v>
-      </c>
-      <c r="F716" s="6">
-        <v>8</v>
-      </c>
-      <c r="G716" s="6">
-        <v>9</v>
-      </c>
-      <c r="H716" s="6">
-        <v>12</v>
-      </c>
-      <c r="I716" s="6">
-        <v>13</v>
-      </c>
-      <c r="J716" s="6">
-        <v>14</v>
-      </c>
-      <c r="K716" s="6">
-        <v>16</v>
-      </c>
-      <c r="L716" s="6">
-        <v>18</v>
-      </c>
-      <c r="M716" s="6">
-        <v>21</v>
-      </c>
-      <c r="N716" s="6">
-        <v>23</v>
-      </c>
-      <c r="O716" s="6">
-        <v>24</v>
-      </c>
-      <c r="P716" s="6">
+      <c r="B716">
+        <v>1</v>
+      </c>
+      <c r="C716">
+        <v>3</v>
+      </c>
+      <c r="D716">
+        <v>6</v>
+      </c>
+      <c r="E716">
+        <v>7</v>
+      </c>
+      <c r="F716">
+        <v>8</v>
+      </c>
+      <c r="G716">
+        <v>9</v>
+      </c>
+      <c r="H716">
+        <v>12</v>
+      </c>
+      <c r="I716">
+        <v>13</v>
+      </c>
+      <c r="J716">
+        <v>14</v>
+      </c>
+      <c r="K716">
+        <v>16</v>
+      </c>
+      <c r="L716">
+        <v>18</v>
+      </c>
+      <c r="M716">
+        <v>21</v>
+      </c>
+      <c r="N716">
+        <v>23</v>
+      </c>
+      <c r="O716">
+        <v>24</v>
+      </c>
+      <c r="P716">
         <v>25</v>
       </c>
     </row>
     <row r="717" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A717" s="5">
+      <c r="A717">
         <v>3787</v>
       </c>
-      <c r="B717" s="6">
-        <v>3</v>
-      </c>
-      <c r="C717" s="6">
-        <v>4</v>
-      </c>
-      <c r="D717" s="6">
-        <v>6</v>
-      </c>
-      <c r="E717" s="6">
-        <v>8</v>
-      </c>
-      <c r="F717" s="6">
-        <v>10</v>
-      </c>
-      <c r="G717" s="6">
-        <v>11</v>
-      </c>
-      <c r="H717" s="6">
-        <v>12</v>
-      </c>
-      <c r="I717" s="6">
-        <v>13</v>
-      </c>
-      <c r="J717" s="6">
-        <v>15</v>
-      </c>
-      <c r="K717" s="6">
-        <v>17</v>
-      </c>
-      <c r="L717" s="6">
-        <v>19</v>
-      </c>
-      <c r="M717" s="6">
-        <v>20</v>
-      </c>
-      <c r="N717" s="6">
-        <v>22</v>
-      </c>
-      <c r="O717" s="6">
-        <v>23</v>
-      </c>
-      <c r="P717" s="6">
+      <c r="B717">
+        <v>3</v>
+      </c>
+      <c r="C717">
+        <v>4</v>
+      </c>
+      <c r="D717">
+        <v>6</v>
+      </c>
+      <c r="E717">
+        <v>8</v>
+      </c>
+      <c r="F717">
+        <v>10</v>
+      </c>
+      <c r="G717">
+        <v>11</v>
+      </c>
+      <c r="H717">
+        <v>12</v>
+      </c>
+      <c r="I717">
+        <v>13</v>
+      </c>
+      <c r="J717">
+        <v>15</v>
+      </c>
+      <c r="K717">
+        <v>17</v>
+      </c>
+      <c r="L717">
+        <v>19</v>
+      </c>
+      <c r="M717">
+        <v>20</v>
+      </c>
+      <c r="N717">
+        <v>22</v>
+      </c>
+      <c r="O717">
+        <v>23</v>
+      </c>
+      <c r="P717">
         <v>24</v>
       </c>
     </row>
     <row r="718" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A718" s="5">
+      <c r="A718">
         <v>3788</v>
       </c>
-      <c r="B718" s="6">
-        <v>1</v>
-      </c>
-      <c r="C718" s="6">
-        <v>4</v>
-      </c>
-      <c r="D718" s="6">
-        <v>5</v>
-      </c>
-      <c r="E718" s="6">
-        <v>7</v>
-      </c>
-      <c r="F718" s="6">
-        <v>8</v>
-      </c>
-      <c r="G718" s="6">
-        <v>9</v>
-      </c>
-      <c r="H718" s="6">
-        <v>12</v>
-      </c>
-      <c r="I718" s="6">
-        <v>16</v>
-      </c>
-      <c r="J718" s="6">
-        <v>17</v>
-      </c>
-      <c r="K718" s="6">
-        <v>18</v>
-      </c>
-      <c r="L718" s="6">
-        <v>20</v>
-      </c>
-      <c r="M718" s="6">
-        <v>21</v>
-      </c>
-      <c r="N718" s="6">
-        <v>22</v>
-      </c>
-      <c r="O718" s="6">
-        <v>23</v>
-      </c>
-      <c r="P718" s="6">
+      <c r="B718">
+        <v>1</v>
+      </c>
+      <c r="C718">
+        <v>4</v>
+      </c>
+      <c r="D718">
+        <v>5</v>
+      </c>
+      <c r="E718">
+        <v>7</v>
+      </c>
+      <c r="F718">
+        <v>8</v>
+      </c>
+      <c r="G718">
+        <v>9</v>
+      </c>
+      <c r="H718">
+        <v>12</v>
+      </c>
+      <c r="I718">
+        <v>16</v>
+      </c>
+      <c r="J718">
+        <v>17</v>
+      </c>
+      <c r="K718">
+        <v>18</v>
+      </c>
+      <c r="L718">
+        <v>20</v>
+      </c>
+      <c r="M718">
+        <v>21</v>
+      </c>
+      <c r="N718">
+        <v>22</v>
+      </c>
+      <c r="O718">
+        <v>23</v>
+      </c>
+      <c r="P718">
         <v>24</v>
       </c>
     </row>
     <row r="719" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A719" s="5">
+      <c r="A719">
         <v>3789</v>
       </c>
-      <c r="B719" s="6">
-        <v>6</v>
-      </c>
-      <c r="C719" s="6">
-        <v>7</v>
-      </c>
-      <c r="D719" s="6">
-        <v>8</v>
-      </c>
-      <c r="E719" s="6">
-        <v>9</v>
-      </c>
-      <c r="F719" s="6">
-        <v>11</v>
-      </c>
-      <c r="G719" s="6">
-        <v>12</v>
-      </c>
-      <c r="H719" s="6">
-        <v>13</v>
-      </c>
-      <c r="I719" s="6">
-        <v>14</v>
-      </c>
-      <c r="J719" s="6">
-        <v>15</v>
-      </c>
-      <c r="K719" s="6">
-        <v>16</v>
-      </c>
-      <c r="L719" s="6">
-        <v>17</v>
-      </c>
-      <c r="M719" s="6">
-        <v>18</v>
-      </c>
-      <c r="N719" s="6">
-        <v>19</v>
-      </c>
-      <c r="O719" s="6">
-        <v>23</v>
-      </c>
-      <c r="P719" s="6">
+      <c r="B719">
+        <v>6</v>
+      </c>
+      <c r="C719">
+        <v>7</v>
+      </c>
+      <c r="D719">
+        <v>8</v>
+      </c>
+      <c r="E719">
+        <v>9</v>
+      </c>
+      <c r="F719">
+        <v>11</v>
+      </c>
+      <c r="G719">
+        <v>12</v>
+      </c>
+      <c r="H719">
+        <v>13</v>
+      </c>
+      <c r="I719">
+        <v>14</v>
+      </c>
+      <c r="J719">
+        <v>15</v>
+      </c>
+      <c r="K719">
+        <v>16</v>
+      </c>
+      <c r="L719">
+        <v>17</v>
+      </c>
+      <c r="M719">
+        <v>18</v>
+      </c>
+      <c r="N719">
+        <v>19</v>
+      </c>
+      <c r="O719">
+        <v>23</v>
+      </c>
+      <c r="P719">
         <v>25</v>
       </c>
     </row>
     <row r="720" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A720" s="5">
+      <c r="A720">
         <v>3790</v>
       </c>
-      <c r="B720" s="6">
-        <v>1</v>
-      </c>
-      <c r="C720" s="6">
-        <v>3</v>
-      </c>
-      <c r="D720" s="6">
-        <v>4</v>
-      </c>
-      <c r="E720" s="6">
-        <v>5</v>
-      </c>
-      <c r="F720" s="6">
-        <v>6</v>
-      </c>
-      <c r="G720" s="6">
-        <v>7</v>
-      </c>
-      <c r="H720" s="6">
-        <v>9</v>
-      </c>
-      <c r="I720" s="6">
-        <v>11</v>
-      </c>
-      <c r="J720" s="6">
-        <v>14</v>
-      </c>
-      <c r="K720" s="6">
-        <v>15</v>
-      </c>
-      <c r="L720" s="6">
-        <v>16</v>
-      </c>
-      <c r="M720" s="6">
-        <v>17</v>
-      </c>
-      <c r="N720" s="6">
-        <v>20</v>
-      </c>
-      <c r="O720" s="6">
-        <v>21</v>
-      </c>
-      <c r="P720" s="6">
+      <c r="B720">
+        <v>1</v>
+      </c>
+      <c r="C720">
+        <v>3</v>
+      </c>
+      <c r="D720">
+        <v>4</v>
+      </c>
+      <c r="E720">
+        <v>5</v>
+      </c>
+      <c r="F720">
+        <v>6</v>
+      </c>
+      <c r="G720">
+        <v>7</v>
+      </c>
+      <c r="H720">
+        <v>9</v>
+      </c>
+      <c r="I720">
+        <v>11</v>
+      </c>
+      <c r="J720">
+        <v>14</v>
+      </c>
+      <c r="K720">
+        <v>15</v>
+      </c>
+      <c r="L720">
+        <v>16</v>
+      </c>
+      <c r="M720">
+        <v>17</v>
+      </c>
+      <c r="N720">
+        <v>20</v>
+      </c>
+      <c r="O720">
+        <v>21</v>
+      </c>
+      <c r="P720">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="721" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A721">
+        <v>3791</v>
+      </c>
+      <c r="B721">
+        <v>1</v>
+      </c>
+      <c r="C721">
+        <v>2</v>
+      </c>
+      <c r="D721">
+        <v>4</v>
+      </c>
+      <c r="E721">
+        <v>6</v>
+      </c>
+      <c r="F721">
+        <v>8</v>
+      </c>
+      <c r="G721">
+        <v>9</v>
+      </c>
+      <c r="H721">
+        <v>11</v>
+      </c>
+      <c r="I721">
+        <v>12</v>
+      </c>
+      <c r="J721">
+        <v>13</v>
+      </c>
+      <c r="K721">
+        <v>14</v>
+      </c>
+      <c r="L721">
+        <v>15</v>
+      </c>
+      <c r="M721">
+        <v>16</v>
+      </c>
+      <c r="N721">
+        <v>19</v>
+      </c>
+      <c r="O721">
+        <v>24</v>
+      </c>
+      <c r="P721">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="722" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A722">
+        <v>3792</v>
+      </c>
+      <c r="B722">
+        <v>2</v>
+      </c>
+      <c r="C722">
+        <v>4</v>
+      </c>
+      <c r="D722">
+        <v>6</v>
+      </c>
+      <c r="E722">
+        <v>7</v>
+      </c>
+      <c r="F722">
+        <v>8</v>
+      </c>
+      <c r="G722">
+        <v>10</v>
+      </c>
+      <c r="H722">
+        <v>11</v>
+      </c>
+      <c r="I722">
+        <v>12</v>
+      </c>
+      <c r="J722">
+        <v>14</v>
+      </c>
+      <c r="K722">
+        <v>15</v>
+      </c>
+      <c r="L722">
+        <v>16</v>
+      </c>
+      <c r="M722">
+        <v>20</v>
+      </c>
+      <c r="N722">
+        <v>23</v>
+      </c>
+      <c r="O722">
+        <v>24</v>
+      </c>
+      <c r="P722">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="723" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A723">
+        <v>3793</v>
+      </c>
+      <c r="B723">
+        <v>1</v>
+      </c>
+      <c r="C723">
+        <v>3</v>
+      </c>
+      <c r="D723">
+        <v>7</v>
+      </c>
+      <c r="E723">
+        <v>8</v>
+      </c>
+      <c r="F723">
+        <v>10</v>
+      </c>
+      <c r="G723">
+        <v>11</v>
+      </c>
+      <c r="H723">
+        <v>13</v>
+      </c>
+      <c r="I723">
+        <v>14</v>
+      </c>
+      <c r="J723">
+        <v>15</v>
+      </c>
+      <c r="K723">
+        <v>17</v>
+      </c>
+      <c r="L723">
+        <v>19</v>
+      </c>
+      <c r="M723">
+        <v>20</v>
+      </c>
+      <c r="N723">
+        <v>21</v>
+      </c>
+      <c r="O723">
+        <v>24</v>
+      </c>
+      <c r="P723">
         <v>25</v>
       </c>
     </row>
@@ -36493,6 +36641,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -36660,16 +36818,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-17T04:03:58+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -36680,6 +36828,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46C5B8C5-4575-4105-836C-9C4A6674A14B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -36699,17 +36858,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0328C38C-FE97-4791-8469-4B5D9CCC5D08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82B637BD-743B-452C-A85E-33AF8B93F052}">
   <ds:schemaRefs>
